--- a/dart_financial_data_by_company/셀바이오휴먼텍_1288410.xlsx
+++ b/dart_financial_data_by_company/셀바이오휴먼텍_1288410.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,137 +461,112 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2023_1분기_thstrm_dt</t>
+          <t>2023_1분기_thstrm_amount</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2023_1분기_thstrm_amount</t>
+          <t>2023_1분기_thstrm_currency</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2023_1분기_thstrm_currency</t>
+          <t>2023_반기_thstrm_amount</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2023_반기_thstrm_dt</t>
+          <t>2023_반기_thstrm_currency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2023_반기_thstrm_amount</t>
+          <t>2023_3분기_thstrm_amount</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2023_반기_thstrm_currency</t>
+          <t>2023_3분기_thstrm_currency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2023_3분기_thstrm_dt</t>
+          <t>2023_사업보고서_thstrm_amount</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>2023_3분기_thstrm_amount</t>
+          <t>2023_사업보고서_thstrm_currency</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>2023_3분기_thstrm_currency</t>
+          <t>2024_1분기_thstrm_amount</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>2023_사업보고서_thstrm_dt</t>
+          <t>2024_1분기_thstrm_currency</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>2023_사업보고서_thstrm_amount</t>
+          <t>2024_반기_thstrm_amount</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>2023_사업보고서_thstrm_currency</t>
+          <t>2024_반기_thstrm_currency</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>2024_1분기_thstrm_dt</t>
+          <t>2024_3분기_thstrm_amount</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>2024_1분기_thstrm_amount</t>
+          <t>2024_3분기_thstrm_currency</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>2024_1분기_thstrm_currency</t>
+          <t>2024_사업보고서_thstrm_amount</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>2024_반기_thstrm_dt</t>
+          <t>2024_사업보고서_thstrm_currency</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>2024_반기_thstrm_amount</t>
+          <t>2025_1분기_thstrm_amount</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>2024_반기_thstrm_currency</t>
+          <t>2025_1분기_thstrm_currency</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>2024_3분기_thstrm_dt</t>
+          <t>2025_반기_thstrm_amount</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>2024_3분기_thstrm_amount</t>
+          <t>2025_반기_thstrm_currency</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>2024_3분기_thstrm_currency</t>
+          <t>2025_3분기_thstrm_amount</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>2024_사업보고서_thstrm_dt</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>2024_사업보고서_thstrm_amount</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>2024_사업보고서_thstrm_currency</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>2025_1분기_thstrm_dt</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>2025_1분기_thstrm_amount</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>2025_1분기_thstrm_currency</t>
+          <t>2025_3분기_thstrm_currency</t>
         </is>
       </c>
     </row>
@@ -628,27 +603,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>499,137,721</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>499,137,721</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,780,886,934</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1,780,886,934</t>
+          <t>432,537,051</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -656,28 +631,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M2" t="n">
+        <v>-1007884017</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>432,537,051</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>647,090,724</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>-1007884017</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>818,563,243</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -686,27 +661,25 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>955,105,199</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>647,090,724</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1957972077</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>818,563,243</t>
+          <t>1,378,290,655</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -714,49 +687,10 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>955,105,199</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>1957972077</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>1,378,290,655</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -791,27 +725,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>499,137,721</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>499,137,721</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,780,886,934</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-1,780,886,934</t>
+          <t>432,537,051</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,28 +753,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M3" t="n">
+        <v>-1007884017</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>432,537,051</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>647,090,724</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1007884017</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>818,563,243</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -849,27 +783,25 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>955,105,199</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>647,090,724</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1957972077</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>818,563,243</t>
+          <t>1,378,290,655</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -879,43 +811,20 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>1,621,279,761</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>955,105,199</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,516,263,611</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>1957972077</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>1,378,290,655</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -954,27 +863,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>5,311,937,992</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5,311,937,992</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>7,261,443,924</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7,261,443,924</t>
+          <t>7,101,241,597</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -982,28 +891,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M4" t="n">
+        <v>7649587496</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7,101,241,597</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>5,956,052,991</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>7649587496</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>7,129,539,995</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1012,27 +921,25 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>7,081,802,792</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>5,956,052,991</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>8251249823</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>7,129,539,995</t>
+          <t>8,288,054,942</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1042,43 +949,20 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>13,987,778,412</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7,081,802,792</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>14,538,872,755</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>8251249823</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>8,288,054,942</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1117,27 +1001,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>699,416,666</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>699,416,666</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,962,146,077</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1,962,146,077</t>
+          <t>605,509,046</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1145,28 +1029,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M5" t="n">
+        <v>-154602128</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>605,509,046</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>1,000,267,469</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>-154602128</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>952,312,727</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1175,27 +1059,25 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>957,884,695</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1,000,267,469</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>2280422476</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>952,312,727</t>
+          <t>1,477,073,573</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1205,43 +1087,20 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>1,833,117,760</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>957,884,695</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,890,529,700</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>2280422476</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>1,477,073,573</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1280,27 +1139,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>559,421,315</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>559,421,315</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>893,674,948</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>893,674,948</t>
+          <t>1,376,528,518</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,28 +1167,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M6" t="n">
+        <v>319770973</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1,376,528,518</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>692,324,229</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>319770973</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>865,297,085</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1338,27 +1197,25 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>1,179,723,020</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>692,324,229</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1299412407</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>865,297,085</t>
+          <t>1,466,686,353</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1368,43 +1225,20 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>3,019,516,279</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1,179,723,020</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,613,146,664</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>1299412407</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>1,466,686,353</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1443,27 +1277,27 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>14,710,545,976</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14,710,545,976</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>9,519,285,234</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9,519,285,234</t>
+          <t>7,735,977,765</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1473,27 +1307,27 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>8,633,700,249</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>7,735,977,765</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>7,942,575,858</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>8,633,700,249</t>
+          <t>8,221,797,569</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1503,27 +1337,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>7,710,516,575</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7,942,575,858</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>6,493,151,730</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>8,221,797,569</t>
+          <t>8,143,976,848</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1533,45 +1367,20 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>7,366,005,134</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7,710,516,575</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>12,051,392,323</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>6,493,151,730</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>8,143,976,848</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1610,27 +1419,27 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>72,254,071</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>72,254,071</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>66,202,702</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>66,202,702</t>
+          <t>61,177,876</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1640,27 +1449,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>74,955,660</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>61,177,876</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>68,382,452</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>74,955,660</t>
+          <t>234,476,265</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1670,27 +1479,27 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>255,646,155</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>68,382,452</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>209,402,999</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>234,476,265</t>
+          <t>170,255,924</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1700,45 +1509,20 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>190,241,162</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>255,646,155</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,381,264,581</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>209,402,999</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>170,255,924</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1777,27 +1561,27 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>26,196,123,040</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>26,196,123,040</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>25,942,958,327</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25,942,958,327</t>
+          <t>25,955,073,944</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1807,27 +1591,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>26,278,187,211</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>25,955,073,944</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>25,905,295,784</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>26,278,187,211</t>
+          <t>26,489,478,868</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1837,27 +1621,27 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>26,996,067,133</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>25,905,295,784</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>28,912,368,236</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>26,489,478,868</t>
+          <t>29,813,965,213</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1867,45 +1651,20 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>28,715,413,376</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26,996,067,133</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>33,264,006,624</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>28,912,368,236</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>29,813,965,213</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -1944,27 +1703,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>14,638,291,905</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14,638,291,905</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>9,453,082,532</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>9,453,082,532</t>
+          <t>7,674,799,889</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1974,27 +1733,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>8,558,744,589</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7,674,799,889</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>7,874,193,406</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8,558,744,589</t>
+          <t>7,987,321,304</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2004,27 +1763,27 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>7,454,870,420</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7,874,193,406</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>6,283,748,731</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>7,987,321,304</t>
+          <t>7,973,720,924</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -2034,45 +1793,20 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>7,175,763,972</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7,454,870,420</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>8,670,127,742</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>6,283,748,731</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>7,973,720,924</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2111,27 +1845,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>20,978,139,142</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20,978,139,142</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>27,610,103,915</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27,610,103,915</t>
+          <t>27,197,113,233</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2141,27 +1875,27 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>26,918,218,987</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>27,197,113,233</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>26,956,596,778</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>26,918,218,987</t>
+          <t>25,863,143,043</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2171,27 +1905,27 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>25,859,733,579</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>26,956,596,778</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>23,992,467,979</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>25,863,143,043</t>
+          <t>25,684,853,461</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2201,45 +1935,20 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>25,585,873,282</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>25,859,733,579</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>30,870,411,984</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>23,992,467,979</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>25,684,853,461</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2278,27 +1987,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>21,585,518,095</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21,585,518,095</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>14,191,362,029</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14,191,362,029</t>
+          <t>14,623,899,080</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2308,27 +2017,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>13,616,015,063</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14,623,899,080</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>14,263,105,787</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>13,616,015,063</t>
+          <t>15,081,669,030</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2338,27 +2047,27 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>16,036,774,229</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14,263,105,787</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>17,994,746,306</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>15,081,669,030</t>
+          <t>19,372,766,020</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2368,45 +2077,20 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>20,990,740,956</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16,036,774,229</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>24,514,944,345</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>17,994,746,306</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>19,372,766,020</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2445,27 +2129,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>4,547,136,000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4,547,136,000</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>4,912,632,500</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4,912,632,500</t>
+          <t>5,077,138,500</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2475,22 +2159,22 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>5,077,138,500</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>5,077,138,500</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2505,22 +2189,22 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>5,077,138,500</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>5,077,138,500</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2535,45 +2219,20 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>5,077,138,500</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5,077,138,500</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>5,117,288,500</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5,077,138,500</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>5,077,138,500</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2612,27 +2271,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>32,463,716,206</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>32,463,716,206</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>44,033,777,008</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>44,033,777,008</t>
+          <t>45,416,209,412</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2642,27 +2301,27 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>44,562,705,949</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>45,416,209,412</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>44,919,316,704</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>44,562,705,949</t>
+          <t>44,130,824,342</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2672,27 +2331,27 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>45,145,284,137</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>44,919,316,704</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>46,411,684,485</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>44,130,824,342</t>
+          <t>47,354,841,826</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2702,45 +2361,20 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>46,935,281,524</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>45,145,284,137</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>52,083,026,285</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>46,411,684,485</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>47,354,841,826</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2779,27 +2413,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>47,174,262,182</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>47,174,262,182</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>53,553,062,242</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>53,553,062,242</t>
+          <t>53,152,187,177</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2809,27 +2443,27 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>53,196,406,198</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>53,152,187,177</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>52,861,892,562</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53,196,406,198</t>
+          <t>52,352,621,911</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2839,27 +2473,27 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>52,855,800,712</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>52,861,892,562</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>52,904,836,215</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>52,352,621,911</t>
+          <t>55,498,818,674</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2869,45 +2503,20 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>54,301,286,658</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>52,855,800,712</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>64,134,418,608</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>52,904,836,215</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>55,498,818,674</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -2946,27 +2555,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>543,786,988</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>543,786,988</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,639,175,677</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-1,639,175,677</t>
+          <t>1,343,411,379</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2974,28 +2583,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M16" t="n">
+        <v>649347702</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1,343,411,379</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>982,558,111</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>649347702</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1,206,104,942</t>
+        </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3004,27 +2613,25 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>-34,776,515</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>982,558,111</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1811385787</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1,206,104,942</t>
+          <t>503,066,886</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -3032,49 +2639,10 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>-34,776,515</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC16" t="n">
-        <v>1811385787</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>503,066,886</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3109,27 +2677,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>543,786,988</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>543,786,988</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,639,175,677</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1,639,175,677</t>
+          <t>1,343,411,379</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3137,28 +2705,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M17" t="n">
+        <v>649347702</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1,343,411,379</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>982,558,111</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>649347702</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1,206,104,942</t>
+        </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3167,27 +2735,25 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>-34,776,515</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>982,558,111</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1811385787</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1,206,104,942</t>
+          <t>503,066,886</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -3197,43 +2763,20 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>413,645,664</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>-34,776,515</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,166,855,719</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>1811385787</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>503,066,886</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -3272,27 +2815,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>5,311,762,167</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5,311,762,167</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>7,257,391,103</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7,257,391,103</t>
+          <t>7,097,313,687</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3300,28 +2843,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M18" t="n">
+        <v>7619311064</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>7,097,313,687</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>5,944,822,364</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>7619311064</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>7,243,461,711</t>
+        </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3330,27 +2873,25 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>6,878,158,476</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5,944,822,364</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>8206221290</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>7,243,461,711</t>
+          <t>8,282,506,329</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3360,43 +2901,20 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>13,858,848,688</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6,878,158,476</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>14,470,237,092</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC18" t="n">
-        <v>8206221290</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>8,282,506,329</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -3435,27 +2953,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>750,848,550</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>750,848,550</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>-1,820,434,820</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-1,820,434,820</t>
+          <t>1,513,793,276</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3463,28 +2981,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M19" t="n">
+        <v>1455999119</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1,513,793,276</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>1,335,734,856</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>1455999119</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1,339,854,426</t>
+        </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3493,27 +3011,25 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>-31,997,019</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1,335,734,856</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>2132164180</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1,339,854,426</t>
+          <t>601,849,804</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3523,43 +3039,20 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>625,483,663</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>-31,997,019</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,541,121,808</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC19" t="n">
-        <v>2132164180</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>601,849,804</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -3598,27 +3091,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.03.31</t>
+          <t>372,925,862</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>372,925,862</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>832,290,236</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>832,290,236</t>
+          <t>1,170,292,234</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3626,28 +3119,28 @@
           <t>KRW</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="M20" t="n">
+        <v>-131694634</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1,170,292,234</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>446,728,699</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>-131694634</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>626,167,383</t>
+        </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3656,27 +3149,25 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>314,935,399</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>446,728,699</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>310209538</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>626,167,383</t>
+          <t>397,146,282</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3686,43 +3177,20 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>1,278,640,566</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>314,935,399</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>1,892,528,670</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC20" t="n">
-        <v>310209538</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>397,146,282</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -3763,30 +3231,38 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2023.01.01 ~ 2023.09.30</t>
-        </is>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1,343,411,379</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>-446040987</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1,343,411,379</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>982,558,111</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2023.01.01 ~ 2023.12.31</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>-446040987</v>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1,206,104,942</t>
+        </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3795,27 +3271,25 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.03.31</t>
+          <t>-34,776,515</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>982,558,111</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1811385787</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.06.30</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1,206,104,942</t>
+          <t>503,066,886</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3825,43 +3299,20 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024.01.01 ~ 2024.09.30</t>
+          <t>413,645,664</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>-34,776,515</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,166,855,719</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
-        <is>
-          <t>2024.01.01 ~ 2024.12.31</t>
-        </is>
-      </c>
-      <c r="AC21" t="n">
-        <v>1811385787</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>2025.01.01 ~ 2025.03.31</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>503,066,886</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -3900,27 +3351,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>8,855,234,628</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8,855,234,628</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,052,311,605</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3,052,311,605</t>
+          <t>2,172,129,845</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3930,27 +3381,27 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>2,575,443,121</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2,172,129,845</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,306,263,592</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2,575,443,121</t>
+          <t>3,979,909,756</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3960,27 +3411,27 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>3,247,720,962</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2,306,263,592</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,796,389,261</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3,979,909,756</t>
+          <t>3,833,009,123</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3990,45 +3441,20 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>2,983,152,587</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3,247,720,962</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>8,127,122,988</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2,796,389,261</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>3,833,009,123</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4067,27 +3493,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>72,254,071</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>72,254,071</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>66,202,702</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>66,202,702</t>
+          <t>61,177,876</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4097,27 +3523,27 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>74,955,660</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>61,177,876</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>68,382,452</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>74,955,660</t>
+          <t>234,476,265</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -4127,27 +3553,27 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>255,646,155</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>68,382,452</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>209,402,999</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>234,476,265</t>
+          <t>170,255,924</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -4157,45 +3583,20 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>161,831,437</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>255,646,155</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>3,273,294,527</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>209,402,999</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>170,255,924</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4234,27 +3635,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>23,085,670,320</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>23,085,670,320</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>22,395,209,176</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22,395,209,176</t>
+          <t>22,217,191,682</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4264,27 +3665,27 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>23,996,875,671</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>22,217,191,682</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>24,068,110,429</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>23,996,875,671</t>
+          <t>25,396,363,779</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -4294,27 +3695,27 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>25,784,749,674</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>24,068,110,429</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>27,581,818,907</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>25,396,363,779</t>
+          <t>28,917,659,228</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -4324,45 +3725,20 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>28,549,730,668</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>25,784,749,674</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>33,249,080,879</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>27,581,818,907</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>28,917,659,228</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4401,27 +3777,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>8,782,980,557</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>8,782,980,557</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,986,108,903</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2,986,108,903</t>
+          <t>2,110,951,969</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4431,27 +3807,27 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>2,500,487,461</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2,110,951,969</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,237,881,140</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2,500,487,461</t>
+          <t>3,745,433,491</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -4461,27 +3837,27 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>2,992,074,807</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2,237,881,140</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>2,586,986,262</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>3,745,433,491</t>
+          <t>3,662,753,199</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -4491,45 +3867,20 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>2,821,321,150</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2,992,074,807</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>4,853,828,461</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2,586,986,262</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>3,662,753,199</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4568,27 +3919,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>18,939,690,950</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18,939,690,950</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>25,512,542,690</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25,512,542,690</t>
+          <t>27,002,810,455</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -4598,27 +3949,27 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>26,275,787,444</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>27,002,810,455</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>26,723,381,268</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>26,275,787,444</t>
+          <t>26,650,430,599</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -4628,27 +3979,27 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>25,319,815,340</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>26,723,381,268</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>24,081,542,928</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>26,650,430,599</t>
+          <t>23,180,989,355</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -4658,45 +4009,20 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>22,055,925,153</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>25,319,815,340</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>26,234,942,398</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>24,081,542,928</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>23,180,989,355</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4735,27 +4061,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>33,170,126,642</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>33,170,126,642</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>44,855,440,261</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>44,855,440,261</t>
+          <t>47,047,872,292</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -4765,27 +4091,27 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>47,697,219,994</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>47,047,872,292</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>48,485,228,105</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>47,697,219,994</t>
+          <t>48,066,884,622</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -4795,27 +4121,27 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>47,856,844,052</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>48,485,228,105</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>48,866,972,574</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>48,066,884,622</t>
+          <t>48,265,639,460</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4825,45 +4151,20 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>47,622,503,234</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>47,856,844,052</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>51,356,900,289</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>48,866,972,574</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>48,265,639,460</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
@@ -4902,27 +4203,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2023.03.31 현재</t>
+          <t>42,025,361,270</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>42,025,361,270</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>47,907,751,866</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2023.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>47,907,751,866</t>
+          <t>49,220,002,137</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -4932,27 +4233,27 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2023.09.30 현재</t>
+          <t>50,272,663,115</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>49,220,002,137</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>50,791,491,697</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2023.12.31 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>50,272,663,115</t>
+          <t>52,046,794,378</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -4962,27 +4263,27 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2024.03.31 현재</t>
+          <t>51,104,565,014</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>50,791,491,697</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>51,663,361,835</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2024.06.30 현재</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>52,046,794,378</t>
+          <t>52,098,648,583</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -4992,45 +4293,20 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024.09.30 현재</t>
+          <t>50,605,655,821</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>51,104,565,014</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>59,484,023,277</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
-        <is>
-          <t>2024.12.31 현재</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>51,663,361,835</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>2025.03.31 현재</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>52,098,648,583</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
